--- a/backend/excel-templates/master_upload_test_data.xlsx
+++ b/backend/excel-templates/master_upload_test_data.xlsx
@@ -433,7 +433,7 @@
         <v>Ram Dahal</v>
       </c>
       <c r="B2" t="str">
-        <v>080MSNCS001</v>
+        <v>080MSNCS01</v>
       </c>
       <c r="C2" t="str">
         <v>Machine Learning for Early Detection of Crop Diseases</v>
@@ -462,7 +462,7 @@
         <v>Shyam Gurung</v>
       </c>
       <c r="B3" t="str">
-        <v>080MSICE002</v>
+        <v>080MSICE02</v>
       </c>
       <c r="C3" t="str">
         <v>Blockchain-Based Land Registry System for Nepal</v>
@@ -491,7 +491,7 @@
         <v>Hari Khadka</v>
       </c>
       <c r="B4" t="str">
-        <v>080MSDSA003</v>
+        <v>080MSDSA03</v>
       </c>
       <c r="C4" t="str">
         <v>Natural Language Processing for Nepali Text Summarization</v>
@@ -520,7 +520,7 @@
         <v>Sita Lama</v>
       </c>
       <c r="B5" t="str">
-        <v>080MSCSKE004</v>
+        <v>080MSCSKE04</v>
       </c>
       <c r="C5" t="str">
         <v>IoT-Enabled Smart Grid for Rural Electrification</v>
@@ -549,7 +549,7 @@
         <v>Gita Maharjan</v>
       </c>
       <c r="B6" t="str">
-        <v>080MSNCS005</v>
+        <v>080MSNCS05</v>
       </c>
       <c r="C6" t="str">
         <v>Deep Learning Approach for Medical Image Diagnosis</v>
@@ -578,7 +578,7 @@
         <v>Rita Neupane</v>
       </c>
       <c r="B7" t="str">
-        <v>080MSICE006</v>
+        <v>080MSICE06</v>
       </c>
       <c r="C7" t="str">
         <v>Cloud Computing Framework for E-Government Services</v>
@@ -607,7 +607,7 @@
         <v>Krishna Ojha</v>
       </c>
       <c r="B8" t="str">
-        <v>080MSDSA007</v>
+        <v>080MSDSA07</v>
       </c>
       <c r="C8" t="str">
         <v>Computer Vision for Traffic Violation Detection</v>
@@ -636,7 +636,7 @@
         <v>Bishnu Pandey</v>
       </c>
       <c r="B9" t="str">
-        <v>080MSCSKE008</v>
+        <v>080MSCSKE08</v>
       </c>
       <c r="C9" t="str">
         <v>Reinforcement Learning for Autonomous Vehicle Navigation</v>
@@ -665,7 +665,7 @@
         <v>Arjun Rai</v>
       </c>
       <c r="B10" t="str">
-        <v>080MSNCS009</v>
+        <v>080MSNCS09</v>
       </c>
       <c r="C10" t="str">
         <v>Big Data Analytics for Tourism Pattern Prediction</v>
@@ -694,7 +694,7 @@
         <v>Pratik Sharma</v>
       </c>
       <c r="B11" t="str">
-        <v>080MSICE010</v>
+        <v>080MSICE10</v>
       </c>
       <c r="C11" t="str">
         <v>Cybersecurity Framework for Financial Transactions</v>
@@ -723,7 +723,7 @@
         <v>Nabin Thapa</v>
       </c>
       <c r="B12" t="str">
-        <v>080MSDSA011</v>
+        <v>080MSDSA11</v>
       </c>
       <c r="C12" t="str">
         <v>Sentiment Analysis of Nepali Social Media Content</v>
@@ -752,7 +752,7 @@
         <v>Sagar Poudel</v>
       </c>
       <c r="B13" t="str">
-        <v>080MSCSKE012</v>
+        <v>080MSCSKE12</v>
       </c>
       <c r="C13" t="str">
         <v>Edge Computing Architecture for Real-Time Monitoring</v>
@@ -781,7 +781,7 @@
         <v>Roshan Pokhrel</v>
       </c>
       <c r="B14" t="str">
-        <v>080MSNCS013</v>
+        <v>080MSNCS13</v>
       </c>
       <c r="C14" t="str">
         <v>Federated Learning for Privacy-Preserving Healthcare</v>
@@ -810,7 +810,7 @@
         <v>Bibek Adhikari</v>
       </c>
       <c r="B15" t="str">
-        <v>080MSICE014</v>
+        <v>080MSICE14</v>
       </c>
       <c r="C15" t="str">
         <v>Optical Character Recognition for Nepali Scripts</v>
@@ -839,7 +839,7 @@
         <v>Amit Bhandari</v>
       </c>
       <c r="B16" t="str">
-        <v>080MSDSA015</v>
+        <v>080MSDSA15</v>
       </c>
       <c r="C16" t="str">
         <v>Wireless Sensor Network for Earthquake Early Warning</v>
@@ -868,7 +868,7 @@
         <v>Sunita Acharya</v>
       </c>
       <c r="B17" t="str">
-        <v>080MSCSKE016</v>
+        <v>080MSCSKE16</v>
       </c>
       <c r="C17" t="str">
         <v>AI-Powered Chatbot for Student Advisory Services</v>
@@ -897,7 +897,7 @@
         <v>Kabita Basnet</v>
       </c>
       <c r="B18" t="str">
-        <v>080MSNCS017</v>
+        <v>080MSNCS17</v>
       </c>
       <c r="C18" t="str">
         <v>Robotic Process Automation in Healthcare Administration</v>
@@ -926,7 +926,7 @@
         <v>Pooja Chhetri</v>
       </c>
       <c r="B19" t="str">
-        <v>080MSICE018</v>
+        <v>080MSICE18</v>
       </c>
       <c r="C19" t="str">
         <v>Augmented Reality for Cultural Heritage Preservation</v>
@@ -955,7 +955,7 @@
         <v>Anita Dahal</v>
       </c>
       <c r="B20" t="str">
-        <v>080MSDSA019</v>
+        <v>080MSDSA19</v>
       </c>
       <c r="C20" t="str">
         <v>Quantum Cryptography for Secure Communications</v>
@@ -984,7 +984,7 @@
         <v>Sarita Gurung</v>
       </c>
       <c r="B21" t="str">
-        <v>080MSCSKE020</v>
+        <v>080MSCSKE20</v>
       </c>
       <c r="C21" t="str">
         <v>Speech Recognition System for Nepali Language</v>
@@ -1013,7 +1013,7 @@
         <v>Deepak Khadka</v>
       </c>
       <c r="B22" t="str">
-        <v>080MSNCS021</v>
+        <v>080MSNCS21</v>
       </c>
       <c r="C22" t="str">
         <v>Smart Waste Management Using IoT Sensors</v>
@@ -1042,7 +1042,7 @@
         <v>Mohan Lama</v>
       </c>
       <c r="B23" t="str">
-        <v>080MSICE022</v>
+        <v>080MSICE22</v>
       </c>
       <c r="C23" t="str">
         <v>Predictive Maintenance Using Machine Learning</v>
@@ -1071,7 +1071,7 @@
         <v>Rajan Maharjan</v>
       </c>
       <c r="B24" t="str">
-        <v>080MSDSA023</v>
+        <v>080MSDSA23</v>
       </c>
       <c r="C24" t="str">
         <v>Recommendation System for E-Learning Platforms</v>
@@ -1100,7 +1100,7 @@
         <v>Umesh Neupane</v>
       </c>
       <c r="B25" t="str">
-        <v>080MSCSKE024</v>
+        <v>080MSCSKE24</v>
       </c>
       <c r="C25" t="str">
         <v>Image Segmentation for Agricultural Land Classification</v>
@@ -1129,7 +1129,7 @@
         <v>Prakash Ojha</v>
       </c>
       <c r="B26" t="str">
-        <v>080MSNCS025</v>
+        <v>080MSNCS25</v>
       </c>
       <c r="C26" t="str">
         <v>Time Series Forecasting for Hydropower Generation</v>
@@ -1158,7 +1158,7 @@
         <v>Mina Pandey</v>
       </c>
       <c r="B27" t="str">
-        <v>080MSICE026</v>
+        <v>080MSICE26</v>
       </c>
       <c r="C27" t="str">
         <v>Mobile Health Application for Remote Patient Monitoring</v>
@@ -1187,7 +1187,7 @@
         <v>Tara Rai</v>
       </c>
       <c r="B28" t="str">
-        <v>080MSDSA027</v>
+        <v>080MSDSA27</v>
       </c>
       <c r="C28" t="str">
         <v>Sustainable Energy Optimization Using AI</v>
@@ -1216,7 +1216,7 @@
         <v>Reema Sharma</v>
       </c>
       <c r="B29" t="str">
-        <v>080MSCSKE028</v>
+        <v>080MSCSKE28</v>
       </c>
       <c r="C29" t="str">
         <v>Automated Essay Scoring in Nepali Education</v>
@@ -1245,7 +1245,7 @@
         <v>Sushma Thapa</v>
       </c>
       <c r="B30" t="str">
-        <v>080MSNCS029</v>
+        <v>080MSNCS29</v>
       </c>
       <c r="C30" t="str">
         <v>Face Recognition System for Attendance Management</v>
@@ -1274,7 +1274,7 @@
         <v>Anjana Poudel</v>
       </c>
       <c r="B31" t="str">
-        <v>080MSICE030</v>
+        <v>080MSICE30</v>
       </c>
       <c r="C31" t="str">
         <v>Gesture Recognition for Human-Computer Interaction</v>
@@ -1303,7 +1303,7 @@
         <v>Ram Pokhrel</v>
       </c>
       <c r="B32" t="str">
-        <v>080MSDSA031</v>
+        <v>080MSDSA31</v>
       </c>
       <c r="C32" t="str">
         <v>Anomaly Detection in Network Traffic Using Deep Learning</v>
@@ -1332,7 +1332,7 @@
         <v>Shyam Adhikari</v>
       </c>
       <c r="B33" t="str">
-        <v>080MSCSKE032</v>
+        <v>080MSCSKE32</v>
       </c>
       <c r="C33" t="str">
         <v>Blockchain for Supply Chain Transparency</v>
@@ -1361,7 +1361,7 @@
         <v>Hari Bhandari</v>
       </c>
       <c r="B34" t="str">
-        <v>080MSNCS033</v>
+        <v>080MSNCS33</v>
       </c>
       <c r="C34" t="str">
         <v>Emotion Recognition from Speech Signals</v>
@@ -1390,7 +1390,7 @@
         <v>Sita Acharya</v>
       </c>
       <c r="B35" t="str">
-        <v>080MSICE034</v>
+        <v>080MSICE34</v>
       </c>
       <c r="C35" t="str">
         <v>Document Classification in Legal Domain</v>
@@ -1419,7 +1419,7 @@
         <v>Gita Basnet</v>
       </c>
       <c r="B36" t="str">
-        <v>080MSDSA035</v>
+        <v>080MSDSA35</v>
       </c>
       <c r="C36" t="str">
         <v>Video Analytics for Crowd Management</v>
@@ -1448,7 +1448,7 @@
         <v>Rita Chhetri</v>
       </c>
       <c r="B37" t="str">
-        <v>080MSCSKE036</v>
+        <v>080MSCSKE36</v>
       </c>
       <c r="C37" t="str">
         <v>Multi-Agent System for Disaster Response</v>
@@ -1477,7 +1477,7 @@
         <v>Krishna Dahal</v>
       </c>
       <c r="B38" t="str">
-        <v>080MSNCS037</v>
+        <v>080MSNCS37</v>
       </c>
       <c r="C38" t="str">
         <v>Knowledge Graph for Research Publication Analysis</v>
@@ -1506,7 +1506,7 @@
         <v>Bishnu Gurung</v>
       </c>
       <c r="B39" t="str">
-        <v>080MSICE038</v>
+        <v>080MSICE38</v>
       </c>
       <c r="C39" t="str">
         <v>Transfer Learning for Low-Resource Nepali NLP</v>
@@ -1535,7 +1535,7 @@
         <v>Arjun Khadka</v>
       </c>
       <c r="B40" t="str">
-        <v>080MSDSA039</v>
+        <v>080MSDSA39</v>
       </c>
       <c r="C40" t="str">
         <v>Explainable AI for Credit Risk Assessment</v>
@@ -1564,7 +1564,7 @@
         <v>Pratik Lama</v>
       </c>
       <c r="B41" t="str">
-        <v>080MSCSKE040</v>
+        <v>080MSCSKE40</v>
       </c>
       <c r="C41" t="str">
         <v>Indoor Localization Using WiFi Fingerprinting</v>
@@ -1593,7 +1593,7 @@
         <v>Nabin Maharjan</v>
       </c>
       <c r="B42" t="str">
-        <v>080MSNCS041</v>
+        <v>080MSNCS41</v>
       </c>
       <c r="C42" t="str">
         <v>Real-Time Sign Language Translation</v>
@@ -1622,7 +1622,7 @@
         <v>Sagar Neupane</v>
       </c>
       <c r="B43" t="str">
-        <v>080MSICE042</v>
+        <v>080MSICE42</v>
       </c>
       <c r="C43" t="str">
         <v>Data Privacy Framework for Social Media Platforms</v>
@@ -1651,7 +1651,7 @@
         <v>Roshan Ojha</v>
       </c>
       <c r="B44" t="str">
-        <v>080MSDSA043</v>
+        <v>080MSDSA43</v>
       </c>
       <c r="C44" t="str">
         <v>Smart Irrigation System Using AI and IoT</v>
@@ -1680,7 +1680,7 @@
         <v>Bibek Pandey</v>
       </c>
       <c r="B45" t="str">
-        <v>080MSCSKE044</v>
+        <v>080MSCSKE44</v>
       </c>
       <c r="C45" t="str">
         <v>Cryptographic Protocol for Secure E-Voting</v>
@@ -1709,7 +1709,7 @@
         <v>Amit Rai</v>
       </c>
       <c r="B46" t="str">
-        <v>080MSNCS045</v>
+        <v>080MSNCS45</v>
       </c>
       <c r="C46" t="str">
         <v>Adaptive Learning System for Personalized Education</v>
@@ -1738,7 +1738,7 @@
         <v>Sunita Sharma</v>
       </c>
       <c r="B47" t="str">
-        <v>080MSICE046</v>
+        <v>080MSICE46</v>
       </c>
       <c r="C47" t="str">
         <v>Digital Twin for Smart Manufacturing</v>
@@ -1767,7 +1767,7 @@
         <v>Kabita Thapa</v>
       </c>
       <c r="B48" t="str">
-        <v>080MSDSA047</v>
+        <v>080MSDSA47</v>
       </c>
       <c r="C48" t="str">
         <v>Social Network Analysis for Misinformation Detection</v>
@@ -1796,7 +1796,7 @@
         <v>Pooja Poudel</v>
       </c>
       <c r="B49" t="str">
-        <v>080MSCSKE048</v>
+        <v>080MSCSKE48</v>
       </c>
       <c r="C49" t="str">
         <v>Autonomous Drone Navigation Using Computer Vision</v>
@@ -1825,7 +1825,7 @@
         <v>Anita Pokhrel</v>
       </c>
       <c r="B50" t="str">
-        <v>080MSNCS049</v>
+        <v>080MSNCS49</v>
       </c>
       <c r="C50" t="str">
         <v>Semantic Web Framework for Heritage Documentation</v>
@@ -1854,7 +1854,7 @@
         <v>Sarita Adhikari</v>
       </c>
       <c r="B51" t="str">
-        <v>080MSICE050</v>
+        <v>080MSICE50</v>
       </c>
       <c r="C51" t="str">
         <v>End-to-End Encryption for Messaging Platforms</v>

--- a/backend/excel-templates/master_upload_test_data.xlsx
+++ b/backend/excel-templates/master_upload_test_data.xlsx
@@ -520,7 +520,7 @@
         <v>Sita Lama</v>
       </c>
       <c r="B5" t="str">
-        <v>080MSCSKE04</v>
+        <v>080MSCSK04</v>
       </c>
       <c r="C5" t="str">
         <v>IoT-Enabled Smart Grid for Rural Electrification</v>
@@ -636,7 +636,7 @@
         <v>Bishnu Pandey</v>
       </c>
       <c r="B9" t="str">
-        <v>080MSCSKE08</v>
+        <v>080MSCSK08</v>
       </c>
       <c r="C9" t="str">
         <v>Reinforcement Learning for Autonomous Vehicle Navigation</v>
@@ -752,7 +752,7 @@
         <v>Sagar Poudel</v>
       </c>
       <c r="B13" t="str">
-        <v>080MSCSKE12</v>
+        <v>080MSCSK12</v>
       </c>
       <c r="C13" t="str">
         <v>Edge Computing Architecture for Real-Time Monitoring</v>
@@ -868,7 +868,7 @@
         <v>Sunita Acharya</v>
       </c>
       <c r="B17" t="str">
-        <v>080MSCSKE16</v>
+        <v>080MSCSK16</v>
       </c>
       <c r="C17" t="str">
         <v>AI-Powered Chatbot for Student Advisory Services</v>
@@ -984,7 +984,7 @@
         <v>Sarita Gurung</v>
       </c>
       <c r="B21" t="str">
-        <v>080MSCSKE20</v>
+        <v>080MSCSK20</v>
       </c>
       <c r="C21" t="str">
         <v>Speech Recognition System for Nepali Language</v>
@@ -1100,7 +1100,7 @@
         <v>Umesh Neupane</v>
       </c>
       <c r="B25" t="str">
-        <v>080MSCSKE24</v>
+        <v>080MSCSK24</v>
       </c>
       <c r="C25" t="str">
         <v>Image Segmentation for Agricultural Land Classification</v>
@@ -1216,7 +1216,7 @@
         <v>Reema Sharma</v>
       </c>
       <c r="B29" t="str">
-        <v>080MSCSKE28</v>
+        <v>080MSCSK28</v>
       </c>
       <c r="C29" t="str">
         <v>Automated Essay Scoring in Nepali Education</v>
@@ -1332,7 +1332,7 @@
         <v>Shyam Adhikari</v>
       </c>
       <c r="B33" t="str">
-        <v>080MSCSKE32</v>
+        <v>080MSCSK32</v>
       </c>
       <c r="C33" t="str">
         <v>Blockchain for Supply Chain Transparency</v>
@@ -1448,7 +1448,7 @@
         <v>Rita Chhetri</v>
       </c>
       <c r="B37" t="str">
-        <v>080MSCSKE36</v>
+        <v>080MSCSK36</v>
       </c>
       <c r="C37" t="str">
         <v>Multi-Agent System for Disaster Response</v>
@@ -1564,7 +1564,7 @@
         <v>Pratik Lama</v>
       </c>
       <c r="B41" t="str">
-        <v>080MSCSKE40</v>
+        <v>080MSCSK40</v>
       </c>
       <c r="C41" t="str">
         <v>Indoor Localization Using WiFi Fingerprinting</v>
@@ -1680,7 +1680,7 @@
         <v>Bibek Pandey</v>
       </c>
       <c r="B45" t="str">
-        <v>080MSCSKE44</v>
+        <v>080MSCSK44</v>
       </c>
       <c r="C45" t="str">
         <v>Cryptographic Protocol for Secure E-Voting</v>
@@ -1796,7 +1796,7 @@
         <v>Pooja Poudel</v>
       </c>
       <c r="B49" t="str">
-        <v>080MSCSKE48</v>
+        <v>080MSCSK48</v>
       </c>
       <c r="C49" t="str">
         <v>Autonomous Drone Navigation Using Computer Vision</v>
